--- a/src/实验器材表.xlsx
+++ b/src/实验器材表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23860"/>
+    <workbookView windowHeight="17120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1474,7 +1474,6 @@
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3"/>
       <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
@@ -1526,7 +1525,6 @@
       <c r="D5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="3"/>
       <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
@@ -1552,7 +1550,6 @@
       <c r="D6" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
         <v>26</v>
       </c>
@@ -1578,7 +1575,6 @@
       <c r="D7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="3"/>
       <c r="F7" s="8" t="s">
         <v>30</v>
       </c>
@@ -1604,7 +1600,6 @@
       <c r="D8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="3"/>
       <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
@@ -1630,7 +1625,6 @@
       <c r="D9" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="3"/>
       <c r="F9" s="8" t="s">
         <v>40</v>
       </c>
@@ -1656,7 +1650,6 @@
       <c r="D10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="3"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
     </row>
@@ -1667,7 +1660,9 @@
       <c r="B11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="10">
+        <v>64.36</v>
+      </c>
       <c r="D11" s="8" t="s">
         <v>45</v>
       </c>
@@ -1687,7 +1682,6 @@
       <c r="D12" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="3"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
     </row>
@@ -1698,7 +1692,9 @@
       <c r="B13" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="10">
+        <v>14.07</v>
+      </c>
       <c r="D13" s="8" t="s">
         <v>50</v>
       </c>
